--- a/experiment_results/combined_sweep/rtt_bursts_S3_atk1pct_wu500000.xlsx
+++ b/experiment_results/combined_sweep/rtt_bursts_S3_atk1pct_wu500000.xlsx
@@ -476,22 +476,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00:010.1</t>
+          <t>00:010.2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>35.4</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -516,12 +516,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>12016</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -533,27 +533,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00:019.9</t>
+          <t>00:019.8</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>26.7</t>
+          <t>114.2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>11.98</t>
+          <t>55.23</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -573,12 +573,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11578</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -595,22 +595,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>129.9</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>17.03</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -652,22 +652,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>14.86</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -704,27 +704,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>00:050.2</t>
+          <t>00:049.8</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -734,12 +734,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>7.10</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -766,22 +766,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>6.94</t>
+          <t>6.84</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -818,27 +818,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>01:010.1</t>
+          <t>01:010.0</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>37.6</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>28.3</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>9.65</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -875,27 +875,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>01:019.7</t>
+          <t>01:020.0</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>22.7</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>4.52</t>
+          <t>10.41</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -932,27 +932,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>01:030.2</t>
+          <t>01:029.6</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>7.07</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -989,27 +989,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>01:040.0</t>
+          <t>01:039.2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>23.3</t>
+          <t>36.3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>7.66</t>
+          <t>15.75</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1046,27 +1046,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>01:050.0</t>
+          <t>01:049.2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>23.3</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>23.9</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>7.39</t>
+          <t>13.84</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1103,27 +1103,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>01:059.9</t>
+          <t>01:059.7</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>33.9</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>6.92</t>
+          <t>8.29</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1160,27 +1160,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>02:009.9</t>
+          <t>02:010.2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1190,12 +1190,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>7.30</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1217,27 +1217,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>02:020.0</t>
+          <t>02:020.8</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>32.7</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1274,27 +1274,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>02:030.0</t>
+          <t>02:028.7</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>33.7</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1304,17 +1304,17 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1331,27 +1331,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>02:039.9</t>
+          <t>02:038.5</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>31.3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1361,12 +1361,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1388,27 +1388,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>02:050.0</t>
+          <t>02:050.6</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>30.4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1445,27 +1445,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>02:054.9</t>
+          <t>02:054.8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">

--- a/experiment_results/combined_sweep/rtt_bursts_S3_atk1pct_wu500000.xlsx
+++ b/experiment_results/combined_sweep/rtt_bursts_S3_atk1pct_wu500000.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,22 +476,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00:010.2</t>
+          <t>00:010.1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>35.4</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -516,12 +516,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>12016</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -533,37 +533,37 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00:019.8</t>
+          <t>00:020.0</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>114.2</t>
+          <t>104.2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>55.23</t>
+          <t>97.23</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>11578</t>
+          <t>34751</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -590,27 +590,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00:029.9</t>
+          <t>00:030.1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>129.9</t>
+          <t>104.7</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>17.03</t>
+          <t>18.99</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -630,12 +630,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>55430</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -647,27 +647,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00:039.9</t>
+          <t>00:040.1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -677,22 +677,22 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>14.86</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>49537</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -704,27 +704,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>00:049.8</t>
+          <t>00:050.1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -734,22 +734,22 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>8.18</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>42409</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -761,27 +761,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>00:059.9</t>
+          <t>01:000.0</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>6.84</t>
+          <t>23.00</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>92383</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -818,27 +818,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>01:010.0</t>
+          <t>01:010.3</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>37.6</t>
+          <t>61.9</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>28.3</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>9.65</t>
+          <t>10.16</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>155976</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -880,22 +880,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>10.41</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>161881</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -932,27 +932,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>01:029.6</t>
+          <t>01:030.0</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>8.80</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>156349</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -989,27 +989,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>01:039.2</t>
+          <t>01:040.2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>36.3</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>15.75</t>
+          <t>8.09</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>125584</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1046,27 +1046,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>01:049.2</t>
+          <t>01:050.1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>35.8</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>13.84</t>
+          <t>7.11</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>88887</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1103,27 +1103,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>01:059.7</t>
+          <t>01:059.9</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>33.9</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>39.8</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>8.29</t>
+          <t>26.46</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>70414</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1160,27 +1160,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>02:010.2</t>
+          <t>02:010.0</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>61.3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1190,22 +1190,22 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>16.98</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>85429</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1217,27 +1217,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>02:020.8</t>
+          <t>02:020.1</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>32.7</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1247,22 +1247,22 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>7.78</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>87085</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1274,27 +1274,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>02:028.7</t>
+          <t>02:030.1</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>33.7</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1304,22 +1304,22 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>9.64</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>78981</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1331,27 +1331,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>02:038.5</t>
+          <t>02:040.2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1361,22 +1361,22 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>11.47</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>61077</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1388,27 +1388,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>02:050.6</t>
+          <t>02:049.9</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>30.4</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18891</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1445,27 +1445,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>02:054.8</t>
+          <t>02:055.1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>34.9</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1494,6 +1494,63 @@
         </is>
       </c>
       <c r="K19" t="inlineStr">
+        <is>
+          <t>Normal/Residual</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>03:000.1</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>35.6</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>20.3</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0.39</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
         <is>
           <t>Normal/Residual</t>
         </is>
